--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/34.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/34.xlsx
@@ -426,13 +426,13 @@
         <v>-22.33371069635794</v>
       </c>
       <c r="E2">
-        <v>-8.825549598730369</v>
+        <v>-12.57815562619256</v>
       </c>
       <c r="F2">
-        <v>1.976340016524739</v>
+        <v>1.045890619321248</v>
       </c>
       <c r="G2">
-        <v>-15.31009902613113</v>
+        <v>-17.44341788218302</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.65007933020853</v>
       </c>
       <c r="E3">
-        <v>-9.95510045588561</v>
+        <v>-12.98943616404319</v>
       </c>
       <c r="F3">
-        <v>2.166636535618028</v>
+        <v>1.344585473502705</v>
       </c>
       <c r="G3">
-        <v>-15.31845153252671</v>
+        <v>-17.91084208323657</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.84481180323053</v>
       </c>
       <c r="E4">
-        <v>-10.6167422077243</v>
+        <v>-12.65143539258468</v>
       </c>
       <c r="F4">
-        <v>1.550624029395461</v>
+        <v>1.737073726820147</v>
       </c>
       <c r="G4">
-        <v>-13.49376987128277</v>
+        <v>-15.43053667284982</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.998831776152</v>
       </c>
       <c r="E5">
-        <v>-11.23178143355006</v>
+        <v>-13.76660834476557</v>
       </c>
       <c r="F5">
-        <v>1.541025187841983</v>
+        <v>1.572354058261206</v>
       </c>
       <c r="G5">
-        <v>-13.6284329321837</v>
+        <v>-16.49107655744642</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.11952261265436</v>
       </c>
       <c r="E6">
-        <v>-11.66982072431201</v>
+        <v>-14.84563048894322</v>
       </c>
       <c r="F6">
-        <v>2.005511879487134</v>
+        <v>1.734653824181356</v>
       </c>
       <c r="G6">
-        <v>-13.63709994040551</v>
+        <v>-16.00987386585843</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.21766410880696</v>
       </c>
       <c r="E7">
-        <v>-12.28466069728143</v>
+        <v>-14.93733208759854</v>
       </c>
       <c r="F7">
-        <v>2.212171248098743</v>
+        <v>1.976149971814886</v>
       </c>
       <c r="G7">
-        <v>-11.68876609272425</v>
+        <v>-15.6468477183858</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.31285288936326</v>
       </c>
       <c r="E8">
-        <v>-12.60370980501784</v>
+        <v>-15.0389691582267</v>
       </c>
       <c r="F8">
-        <v>2.158030677673529</v>
+        <v>1.61622904694254</v>
       </c>
       <c r="G8">
-        <v>-12.63305948125488</v>
+        <v>-14.19137961422738</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.42137404567563</v>
       </c>
       <c r="E9">
-        <v>-13.64659925508829</v>
+        <v>-16.21544406304942</v>
       </c>
       <c r="F9">
-        <v>2.113658405334747</v>
+        <v>1.713455920503199</v>
       </c>
       <c r="G9">
-        <v>-11.51313172022929</v>
+        <v>-14.34222793226981</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.53463290818927</v>
       </c>
       <c r="E10">
-        <v>-14.11947156791725</v>
+        <v>-18.23741223594824</v>
       </c>
       <c r="F10">
-        <v>2.145375283703253</v>
+        <v>1.804647290820118</v>
       </c>
       <c r="G10">
-        <v>-11.13442186326436</v>
+        <v>-12.74634966015428</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.6721784929505</v>
       </c>
       <c r="E11">
-        <v>-14.01273543555646</v>
+        <v>-16.72409132053897</v>
       </c>
       <c r="F11">
-        <v>2.662254134442972</v>
+        <v>2.019147587419067</v>
       </c>
       <c r="G11">
-        <v>-11.25213493100423</v>
+        <v>-12.37580360848919</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.83634739677288</v>
       </c>
       <c r="E12">
-        <v>-14.63909131792738</v>
+        <v>-16.6867359384497</v>
       </c>
       <c r="F12">
-        <v>2.15293272833173</v>
+        <v>1.75360603287142</v>
       </c>
       <c r="G12">
-        <v>-9.939910821784533</v>
+        <v>-12.60598252928918</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.01566098278257</v>
       </c>
       <c r="E13">
-        <v>-15.63337665647351</v>
+        <v>-20.64357614365782</v>
       </c>
       <c r="F13">
-        <v>2.759134176408149</v>
+        <v>2.296053815615908</v>
       </c>
       <c r="G13">
-        <v>-9.731518601178491</v>
+        <v>-12.36787816246818</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.2263616185402</v>
       </c>
       <c r="E14">
-        <v>-16.89248262651419</v>
+        <v>-20.87602271447154</v>
       </c>
       <c r="F14">
-        <v>2.944434103338226</v>
+        <v>2.732624523089608</v>
       </c>
       <c r="G14">
-        <v>-8.811488200905174</v>
+        <v>-11.62745478933694</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.46843348965066</v>
       </c>
       <c r="E15">
-        <v>-17.80849782031174</v>
+        <v>-20.45857892349647</v>
       </c>
       <c r="F15">
-        <v>3.007042749293294</v>
+        <v>2.57851251675228</v>
       </c>
       <c r="G15">
-        <v>-8.709235380833706</v>
+        <v>-11.58692378029965</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.73110667229928</v>
       </c>
       <c r="E16">
-        <v>-19.27079189060258</v>
+        <v>-21.93517844317754</v>
       </c>
       <c r="F16">
-        <v>3.514774114665435</v>
+        <v>3.132199860378643</v>
       </c>
       <c r="G16">
-        <v>-7.917429030387441</v>
+        <v>-11.18703305297446</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.02765754133815</v>
       </c>
       <c r="E17">
-        <v>-19.42345127787516</v>
+        <v>-23.43471015523346</v>
       </c>
       <c r="F17">
-        <v>3.817730721465339</v>
+        <v>3.070855011744095</v>
       </c>
       <c r="G17">
-        <v>-8.655498605640256</v>
+        <v>-10.35080580248226</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.357005462394541</v>
       </c>
       <c r="E18">
-        <v>-21.58732824075235</v>
+        <v>-24.42037327926898</v>
       </c>
       <c r="F18">
-        <v>3.966990252877761</v>
+        <v>3.33016785092632</v>
       </c>
       <c r="G18">
-        <v>-8.085958972155119</v>
+        <v>-9.420075719026014</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.711398837017635</v>
       </c>
       <c r="E19">
-        <v>-21.79493160315999</v>
+        <v>-24.27009134085043</v>
       </c>
       <c r="F19">
-        <v>4.121263797218464</v>
+        <v>3.498607644680629</v>
       </c>
       <c r="G19">
-        <v>-7.076878207420947</v>
+        <v>-10.32809546008285</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.101613222282269</v>
       </c>
       <c r="E20">
-        <v>-22.55379969194336</v>
+        <v>-25.42765080974311</v>
       </c>
       <c r="F20">
-        <v>4.207418982724285</v>
+        <v>3.75522660010069</v>
       </c>
       <c r="G20">
-        <v>-7.192128229279595</v>
+        <v>-9.297820582806269</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.524615934331412</v>
       </c>
       <c r="E21">
-        <v>-23.68911076803636</v>
+        <v>-26.54334453643488</v>
       </c>
       <c r="F21">
-        <v>4.215312173006835</v>
+        <v>4.118018783797728</v>
       </c>
       <c r="G21">
-        <v>-7.51052656761008</v>
+        <v>-9.547197357188489</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.973962882677593</v>
       </c>
       <c r="E22">
-        <v>-24.22967923880598</v>
+        <v>-24.94455773107885</v>
       </c>
       <c r="F22">
-        <v>4.175420204702831</v>
+        <v>3.479961091232244</v>
       </c>
       <c r="G22">
-        <v>-6.328148675531679</v>
+        <v>-7.645338603060281</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.461219606333914</v>
       </c>
       <c r="E23">
-        <v>-23.59492303715082</v>
+        <v>-26.83463409850427</v>
       </c>
       <c r="F23">
-        <v>4.820990998131159</v>
+        <v>3.918452833981372</v>
       </c>
       <c r="G23">
-        <v>-6.639806743144208</v>
+        <v>-8.037972614563383</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.991010972397234</v>
       </c>
       <c r="E24">
-        <v>-25.18402796507846</v>
+        <v>-26.40027192863654</v>
       </c>
       <c r="F24">
-        <v>4.730943063485188</v>
+        <v>3.609243756227313</v>
       </c>
       <c r="G24">
-        <v>-6.124659372869298</v>
+        <v>-8.12724147502983</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.566998468872008</v>
       </c>
       <c r="E25">
-        <v>-24.64894347633213</v>
+        <v>-28.07627374429737</v>
       </c>
       <c r="F25">
-        <v>4.487036515448358</v>
+        <v>3.848483122931342</v>
       </c>
       <c r="G25">
-        <v>-5.252337244362418</v>
+        <v>-7.277626378376813</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.205249342940308</v>
       </c>
       <c r="E26">
-        <v>-25.80020836635415</v>
+        <v>-29.33155315380156</v>
       </c>
       <c r="F26">
-        <v>4.743584204102225</v>
+        <v>3.489382557723194</v>
       </c>
       <c r="G26">
-        <v>-5.706719551264007</v>
+        <v>-8.321593672003825</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.914722138200574</v>
       </c>
       <c r="E27">
-        <v>-25.02442642715213</v>
+        <v>-26.65046106061232</v>
       </c>
       <c r="F27">
-        <v>4.629098103475108</v>
+        <v>3.742582292071822</v>
       </c>
       <c r="G27">
-        <v>-4.795690524311969</v>
+        <v>-6.183414935100283</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.698313714513451</v>
       </c>
       <c r="E28">
-        <v>-26.19716534091852</v>
+        <v>-27.69669252450043</v>
       </c>
       <c r="F28">
-        <v>4.389477063645457</v>
+        <v>3.890758568638083</v>
       </c>
       <c r="G28">
-        <v>-5.577740697054001</v>
+        <v>-7.381607303219782</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.562436252853926</v>
       </c>
       <c r="E29">
-        <v>-25.47015506677911</v>
+        <v>-28.21482693503605</v>
       </c>
       <c r="F29">
-        <v>4.320967529449462</v>
+        <v>3.622439193914754</v>
       </c>
       <c r="G29">
-        <v>-5.431931029322341</v>
+        <v>-6.377426145883731</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.505448866075961</v>
       </c>
       <c r="E30">
-        <v>-25.24820097024116</v>
+        <v>-27.32247301792857</v>
       </c>
       <c r="F30">
-        <v>4.364199533529129</v>
+        <v>3.224376295774965</v>
       </c>
       <c r="G30">
-        <v>-5.544204870741184</v>
+        <v>-6.453509103467261</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.519533088993143</v>
       </c>
       <c r="E31">
-        <v>-25.95772227776295</v>
+        <v>-27.33918308701688</v>
       </c>
       <c r="F31">
-        <v>4.236011209321629</v>
+        <v>3.265603328165684</v>
       </c>
       <c r="G31">
-        <v>-4.820837428228272</v>
+        <v>-7.350938409343973</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.599664303310363</v>
       </c>
       <c r="E32">
-        <v>-25.67287673420648</v>
+        <v>-27.39874610563977</v>
       </c>
       <c r="F32">
-        <v>3.954417211615087</v>
+        <v>3.302395983993174</v>
       </c>
       <c r="G32">
-        <v>-5.654204367374548</v>
+        <v>-6.534696922272348</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.737230521001345</v>
       </c>
       <c r="E33">
-        <v>-24.33915962641542</v>
+        <v>-26.50728882638581</v>
       </c>
       <c r="F33">
-        <v>4.062566904874531</v>
+        <v>3.000932811871528</v>
       </c>
       <c r="G33">
-        <v>-5.319991553002964</v>
+        <v>-6.899628288702829</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.918244209644676</v>
       </c>
       <c r="E34">
-        <v>-24.81375275936729</v>
+        <v>-27.71088929051448</v>
       </c>
       <c r="F34">
-        <v>4.300974825972955</v>
+        <v>3.077588929296544</v>
       </c>
       <c r="G34">
-        <v>-4.333220554657941</v>
+        <v>-6.878712261985713</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.131234233736262</v>
       </c>
       <c r="E35">
-        <v>-24.74039148044303</v>
+        <v>-26.65800096983509</v>
       </c>
       <c r="F35">
-        <v>4.021582179488874</v>
+        <v>3.134472478367298</v>
       </c>
       <c r="G35">
-        <v>-4.556924048383112</v>
+        <v>-6.223320251030657</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.365776720189682</v>
       </c>
       <c r="E36">
-        <v>-24.3646504066046</v>
+        <v>-27.56440221331436</v>
       </c>
       <c r="F36">
-        <v>3.979325738253118</v>
+        <v>3.093115582091512</v>
       </c>
       <c r="G36">
-        <v>-5.298813993188246</v>
+        <v>-6.441213737334408</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.608783784722857</v>
       </c>
       <c r="E37">
-        <v>-24.03969164028818</v>
+        <v>-25.42010637204633</v>
       </c>
       <c r="F37">
-        <v>4.09717563024463</v>
+        <v>3.191230914670732</v>
       </c>
       <c r="G37">
-        <v>-4.640416006883532</v>
+        <v>-7.628785875363925</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.852037014093611</v>
       </c>
       <c r="E38">
-        <v>-22.86747802950667</v>
+        <v>-26.05411990396423</v>
       </c>
       <c r="F38">
-        <v>4.056596333573324</v>
+        <v>3.387092576350875</v>
       </c>
       <c r="G38">
-        <v>-5.50629250322545</v>
+        <v>-6.652208046734318</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.092961089187961</v>
       </c>
       <c r="E39">
-        <v>-22.38193504640426</v>
+        <v>-25.618870153191</v>
       </c>
       <c r="F39">
-        <v>4.25722495005894</v>
+        <v>3.205614131794754</v>
       </c>
       <c r="G39">
-        <v>-5.944827228630547</v>
+        <v>-6.843696621816842</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.327578051274726</v>
       </c>
       <c r="E40">
-        <v>-22.66731042141963</v>
+        <v>-25.5069942028315</v>
       </c>
       <c r="F40">
-        <v>3.807558578370471</v>
+        <v>3.560766518155711</v>
       </c>
       <c r="G40">
-        <v>-4.896301313795959</v>
+        <v>-7.858269581600664</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.557304930321354</v>
       </c>
       <c r="E41">
-        <v>-22.05022885381641</v>
+        <v>-25.16882587783471</v>
       </c>
       <c r="F41">
-        <v>4.40298132398641</v>
+        <v>3.751504891199408</v>
       </c>
       <c r="G41">
-        <v>-5.851161963687947</v>
+        <v>-6.946737351726657</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.789599063971483</v>
       </c>
       <c r="E42">
-        <v>-22.68109509629898</v>
+        <v>-23.82636428673484</v>
       </c>
       <c r="F42">
-        <v>3.961279409346686</v>
+        <v>3.512284528966364</v>
       </c>
       <c r="G42">
-        <v>-5.748455598877598</v>
+        <v>-8.561820098515499</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.027686525428669</v>
       </c>
       <c r="E43">
-        <v>-21.37651871874728</v>
+        <v>-21.50602854689264</v>
       </c>
       <c r="F43">
-        <v>4.070439506980181</v>
+        <v>3.492157210487044</v>
       </c>
       <c r="G43">
-        <v>-5.446758962792736</v>
+        <v>-7.360108620487754</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.277265636098988</v>
       </c>
       <c r="E44">
-        <v>-20.51471388729555</v>
+        <v>-22.20092288336966</v>
       </c>
       <c r="F44">
-        <v>4.270713373340738</v>
+        <v>3.412195898816506</v>
       </c>
       <c r="G44">
-        <v>-6.105368824011964</v>
+        <v>-8.394458779323184</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.547057594303621</v>
       </c>
       <c r="E45">
-        <v>-20.03107739175036</v>
+        <v>-22.23647593280388</v>
       </c>
       <c r="F45">
-        <v>4.34878057273641</v>
+        <v>3.310154559272911</v>
       </c>
       <c r="G45">
-        <v>-6.26882369946794</v>
+        <v>-7.973552708914705</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.837523892645196</v>
       </c>
       <c r="E46">
-        <v>-18.56054602723957</v>
+        <v>-21.48176045468554</v>
       </c>
       <c r="F46">
-        <v>4.281667867157832</v>
+        <v>3.087922610394787</v>
       </c>
       <c r="G46">
-        <v>-6.154513872542445</v>
+        <v>-8.883674646388982</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.150579163168803</v>
       </c>
       <c r="E47">
-        <v>-18.97693015529684</v>
+        <v>-20.47957292899603</v>
       </c>
       <c r="F47">
-        <v>4.347686231948841</v>
+        <v>3.493261053510105</v>
       </c>
       <c r="G47">
-        <v>-6.932068324442147</v>
+        <v>-8.569679333625729</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.490149383997458</v>
       </c>
       <c r="E48">
-        <v>-18.95487648687948</v>
+        <v>-19.67983989076743</v>
       </c>
       <c r="F48">
-        <v>4.844942966396265</v>
+        <v>3.892730282502805</v>
       </c>
       <c r="G48">
-        <v>-6.513956354468814</v>
+        <v>-8.368408096474658</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.851276623131909</v>
       </c>
       <c r="E49">
-        <v>-17.49517270372103</v>
+        <v>-21.43884863498885</v>
       </c>
       <c r="F49">
-        <v>4.43340114721017</v>
+        <v>3.868461573054611</v>
       </c>
       <c r="G49">
-        <v>-6.91406557779959</v>
+        <v>-9.595720023157586</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.231400545109164</v>
       </c>
       <c r="E50">
-        <v>-17.06002710784998</v>
+        <v>-19.55249920167174</v>
       </c>
       <c r="F50">
-        <v>4.622226403508016</v>
+        <v>3.720467422668625</v>
       </c>
       <c r="G50">
-        <v>-6.512208386424079</v>
+        <v>-9.517389205152892</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.628859633469389</v>
       </c>
       <c r="E51">
-        <v>-16.7600066478938</v>
+        <v>-18.97595200491119</v>
       </c>
       <c r="F51">
-        <v>4.526366268152382</v>
+        <v>3.547420628406303</v>
       </c>
       <c r="G51">
-        <v>-7.315561919711321</v>
+        <v>-9.350941596529415</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.03257934082783</v>
       </c>
       <c r="E52">
-        <v>-16.31135261405787</v>
+        <v>-18.34134977137229</v>
       </c>
       <c r="F52">
-        <v>4.488058005763817</v>
+        <v>4.24554987005032</v>
       </c>
       <c r="G52">
-        <v>-7.274809104122893</v>
+        <v>-9.305405042636739</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.43569825208221</v>
       </c>
       <c r="E53">
-        <v>-16.66171611955732</v>
+        <v>-18.58940599209045</v>
       </c>
       <c r="F53">
-        <v>4.50120434856788</v>
+        <v>4.456995197938387</v>
       </c>
       <c r="G53">
-        <v>-7.178819836211725</v>
+        <v>-9.659090485870315</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.83288210036228</v>
       </c>
       <c r="E54">
-        <v>-15.29062098730695</v>
+        <v>-18.07058325350566</v>
       </c>
       <c r="F54">
-        <v>4.834086662345928</v>
+        <v>4.215986831726812</v>
       </c>
       <c r="G54">
-        <v>-7.65715394008994</v>
+        <v>-9.768742375222056</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.2115891621579</v>
       </c>
       <c r="E55">
-        <v>-14.79179146146603</v>
+        <v>-17.83306479180336</v>
       </c>
       <c r="F55">
-        <v>4.375152443640308</v>
+        <v>4.033247757262001</v>
       </c>
       <c r="G55">
-        <v>-8.179637479279876</v>
+        <v>-10.21310035023073</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.56653334845501</v>
       </c>
       <c r="E56">
-        <v>-14.16605145156015</v>
+        <v>-16.48065414330863</v>
       </c>
       <c r="F56">
-        <v>4.619290212740791</v>
+        <v>3.860516120476851</v>
       </c>
       <c r="G56">
-        <v>-7.665900401404695</v>
+        <v>-10.98876779117305</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.89480847492151</v>
       </c>
       <c r="E57">
-        <v>-13.90112213668941</v>
+        <v>-18.19518874430072</v>
       </c>
       <c r="F57">
-        <v>4.777765328875155</v>
+        <v>4.104140768860733</v>
       </c>
       <c r="G57">
-        <v>-8.150173623980363</v>
+        <v>-9.654631181028918</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.1884771761371</v>
       </c>
       <c r="E58">
-        <v>-13.47291869147211</v>
+        <v>-17.96761933999326</v>
       </c>
       <c r="F58">
-        <v>4.322696936309122</v>
+        <v>3.637717204880999</v>
       </c>
       <c r="G58">
-        <v>-8.141973402679588</v>
+        <v>-11.01087230373876</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.44821032302854</v>
       </c>
       <c r="E59">
-        <v>-13.67036921515455</v>
+        <v>-15.64720208761893</v>
       </c>
       <c r="F59">
-        <v>4.622285000626887</v>
+        <v>4.239660067750801</v>
       </c>
       <c r="G59">
-        <v>-7.787605987064921</v>
+        <v>-11.70906635797106</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.67491923998414</v>
       </c>
       <c r="E60">
-        <v>-13.67095338830154</v>
+        <v>-17.29225178343732</v>
       </c>
       <c r="F60">
-        <v>4.521022844393689</v>
+        <v>3.790863150609909</v>
       </c>
       <c r="G60">
-        <v>-8.228074071064952</v>
+        <v>-11.05031745383918</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.86461674247776</v>
       </c>
       <c r="E61">
-        <v>-13.36295375714385</v>
+        <v>-15.43430493909632</v>
       </c>
       <c r="F61">
-        <v>4.440139815880365</v>
+        <v>3.635520604776284</v>
       </c>
       <c r="G61">
-        <v>-8.045136635110365</v>
+        <v>-11.67153801373788</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.02152929614346</v>
       </c>
       <c r="E62">
-        <v>-13.69487278801006</v>
+        <v>-15.76767761011899</v>
       </c>
       <c r="F62">
-        <v>4.651757767713215</v>
+        <v>3.63193826199556</v>
       </c>
       <c r="G62">
-        <v>-8.347677460307743</v>
+        <v>-11.44092872201779</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.14794334140694</v>
       </c>
       <c r="E63">
-        <v>-12.85317890962639</v>
+        <v>-15.64444424694826</v>
       </c>
       <c r="F63">
-        <v>4.445609936112293</v>
+        <v>4.290188204982897</v>
       </c>
       <c r="G63">
-        <v>-8.123924308399481</v>
+        <v>-12.00577731247377</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.24184378013726</v>
       </c>
       <c r="E64">
-        <v>-12.40390900332542</v>
+        <v>-14.6190256495994</v>
       </c>
       <c r="F64">
-        <v>4.742869952734362</v>
+        <v>4.272979656505732</v>
       </c>
       <c r="G64">
-        <v>-9.616596323328231</v>
+        <v>-11.88211850494538</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.30915874593188</v>
       </c>
       <c r="E65">
-        <v>-13.48335229558579</v>
+        <v>-15.69104224448718</v>
       </c>
       <c r="F65">
-        <v>4.526437534918577</v>
+        <v>3.74410740086839</v>
       </c>
       <c r="G65">
-        <v>-8.757827568259128</v>
+        <v>-11.03054025478757</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.35128471006687</v>
       </c>
       <c r="E66">
-        <v>-12.04655353395813</v>
+        <v>-15.13202929908432</v>
       </c>
       <c r="F66">
-        <v>4.849993404560601</v>
+        <v>3.522276129586871</v>
       </c>
       <c r="G66">
-        <v>-8.963402514611252</v>
+        <v>-11.03963763392949</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.366790831825</v>
       </c>
       <c r="E67">
-        <v>-12.40168099411364</v>
+        <v>-15.19568152973614</v>
       </c>
       <c r="F67">
-        <v>4.584179452595499</v>
+        <v>4.314711891083476</v>
       </c>
       <c r="G67">
-        <v>-9.011501430751322</v>
+        <v>-11.41300758093957</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.36208004088235</v>
       </c>
       <c r="E68">
-        <v>-10.96471015047369</v>
+        <v>-16.97286304015034</v>
       </c>
       <c r="F68">
-        <v>4.220286593287231</v>
+        <v>3.983246994099746</v>
       </c>
       <c r="G68">
-        <v>-8.947316573835932</v>
+        <v>-11.76629906925398</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.33744893924076</v>
       </c>
       <c r="E69">
-        <v>-11.98162880211016</v>
+        <v>-14.19659600874188</v>
       </c>
       <c r="F69">
-        <v>4.392150359230719</v>
+        <v>3.720689141496787</v>
       </c>
       <c r="G69">
-        <v>-9.289299238588185</v>
+        <v>-11.22446208084146</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.2919828942512</v>
       </c>
       <c r="E70">
-        <v>-11.84533984837531</v>
+        <v>-15.42647520753706</v>
       </c>
       <c r="F70">
-        <v>4.282437548232736</v>
+        <v>4.309108739554651</v>
       </c>
       <c r="G70">
-        <v>-9.562823132133849</v>
+        <v>-10.46141443949485</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.23241135863181</v>
       </c>
       <c r="E71">
-        <v>-12.09754415128449</v>
+        <v>-15.25093344110372</v>
       </c>
       <c r="F71">
-        <v>4.08943130831813</v>
+        <v>3.354335203195926</v>
       </c>
       <c r="G71">
-        <v>-8.439286876470455</v>
+        <v>-11.34578695376467</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.15821828841551</v>
       </c>
       <c r="E72">
-        <v>-12.2788551936036</v>
+        <v>-14.20199847823303</v>
       </c>
       <c r="F72">
-        <v>4.130886394360673</v>
+        <v>3.587651509776212</v>
       </c>
       <c r="G72">
-        <v>-8.616953923926522</v>
+        <v>-11.47123014533874</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.06925132574571</v>
       </c>
       <c r="E73">
-        <v>-12.32584263990719</v>
+        <v>-15.00391876940733</v>
       </c>
       <c r="F73">
-        <v>3.712691426623818</v>
+        <v>3.354539501259017</v>
       </c>
       <c r="G73">
-        <v>-8.536044190946733</v>
+        <v>-9.415116521808187</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.97287923147957</v>
       </c>
       <c r="E74">
-        <v>-12.2957418731782</v>
+        <v>-14.7156768703451</v>
       </c>
       <c r="F74">
-        <v>3.792918800888149</v>
+        <v>3.345190885240178</v>
       </c>
       <c r="G74">
-        <v>-8.927244736231332</v>
+        <v>-10.20279462196698</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.86834617733118</v>
       </c>
       <c r="E75">
-        <v>-12.78027500657691</v>
+        <v>-13.79062737090225</v>
       </c>
       <c r="F75">
-        <v>4.056818052401486</v>
+        <v>3.356264157000931</v>
       </c>
       <c r="G75">
-        <v>-7.915399665971868</v>
+        <v>-10.96520332802452</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.75619622431944</v>
       </c>
       <c r="E76">
-        <v>-12.36838765320925</v>
+        <v>-14.27680434036574</v>
       </c>
       <c r="F76">
-        <v>3.710032384391795</v>
+        <v>3.181936144653018</v>
       </c>
       <c r="G76">
-        <v>-7.626879001133305</v>
+        <v>-10.73075711402441</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.64398551795551</v>
       </c>
       <c r="E77">
-        <v>-13.58792381737091</v>
+        <v>-16.1353172439577</v>
       </c>
       <c r="F77">
-        <v>3.542313176829011</v>
+        <v>2.933525536992679</v>
       </c>
       <c r="G77">
-        <v>-8.216146175486958</v>
+        <v>-10.47734809517536</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.52998597469643</v>
       </c>
       <c r="E78">
-        <v>-12.74704053583461</v>
+        <v>-16.66178857514144</v>
       </c>
       <c r="F78">
-        <v>3.935689889165015</v>
+        <v>3.304492810625216</v>
       </c>
       <c r="G78">
-        <v>-7.577601530781253</v>
+        <v>-11.06027888536685</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.41417860119996</v>
       </c>
       <c r="E79">
-        <v>-13.59281004082519</v>
+        <v>-17.36860638368065</v>
       </c>
       <c r="F79">
-        <v>3.476543453866726</v>
+        <v>3.207474986245395</v>
       </c>
       <c r="G79">
-        <v>-7.824270278912349</v>
+        <v>-9.790145052133445</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.30286868065426</v>
       </c>
       <c r="E80">
-        <v>-13.62652000133828</v>
+        <v>-17.14555186795884</v>
       </c>
       <c r="F80">
-        <v>3.865998910356102</v>
+        <v>3.455486500015043</v>
       </c>
       <c r="G80">
-        <v>-8.200202588169828</v>
+        <v>-9.52465916315713</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.19223722533699</v>
       </c>
       <c r="E81">
-        <v>-14.68956116074287</v>
+        <v>-19.56897379011165</v>
       </c>
       <c r="F81">
-        <v>3.743434325854328</v>
+        <v>2.852438210416264</v>
       </c>
       <c r="G81">
-        <v>-8.132213914429816</v>
+        <v>-9.114363391202017</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.08100663002896</v>
       </c>
       <c r="E82">
-        <v>-17.59341794731744</v>
+        <v>-19.33553095501624</v>
       </c>
       <c r="F82">
-        <v>3.825389523272404</v>
+        <v>3.249322831354967</v>
       </c>
       <c r="G82">
-        <v>-6.898131922119078</v>
+        <v>-8.950713193559224</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.97400601708408</v>
       </c>
       <c r="E83">
-        <v>-16.3884181847204</v>
+        <v>-17.82369990755549</v>
       </c>
       <c r="F83">
-        <v>3.782776748205675</v>
+        <v>2.938632988569971</v>
       </c>
       <c r="G83">
-        <v>-7.622956004669269</v>
+        <v>-9.624690607171749</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.86586958037506</v>
       </c>
       <c r="E84">
-        <v>-18.26094218689209</v>
+        <v>-19.66610050062816</v>
       </c>
       <c r="F84">
-        <v>3.497860135488541</v>
+        <v>2.486801690895097</v>
       </c>
       <c r="G84">
-        <v>-6.255674212585954</v>
+        <v>-8.466423418255861</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.75508950364683</v>
       </c>
       <c r="E85">
-        <v>-19.32176892250693</v>
+        <v>-21.35181136456143</v>
       </c>
       <c r="F85">
-        <v>3.538713413283217</v>
+        <v>3.217415908276609</v>
       </c>
       <c r="G85">
-        <v>-6.889544366990209</v>
+        <v>-8.449705163282541</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.64683278127559</v>
       </c>
       <c r="E86">
-        <v>-20.87024891011175</v>
+        <v>-22.506943571386</v>
       </c>
       <c r="F86">
-        <v>3.464792355974165</v>
+        <v>2.989401849101214</v>
       </c>
       <c r="G86">
-        <v>-6.432963857850544</v>
+        <v>-7.456415700770693</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.53624350558265</v>
       </c>
       <c r="E87">
-        <v>-21.23024447982552</v>
+        <v>-22.60308307456884</v>
       </c>
       <c r="F87">
-        <v>3.492887298914061</v>
+        <v>3.518058720734056</v>
       </c>
       <c r="G87">
-        <v>-6.590241255330239</v>
+        <v>-7.721375213006262</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.4231496036082</v>
       </c>
       <c r="E88">
-        <v>-22.72985770441357</v>
+        <v>-24.83831067391088</v>
       </c>
       <c r="F88">
-        <v>3.333957659181966</v>
+        <v>3.047823176615859</v>
       </c>
       <c r="G88">
-        <v>-6.069353399090232</v>
+        <v>-7.156046593447078</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.31212216995079</v>
       </c>
       <c r="E89">
-        <v>-25.80524402945068</v>
+        <v>-26.51436230278579</v>
       </c>
       <c r="F89">
-        <v>3.359445822185049</v>
+        <v>3.006740261463445</v>
       </c>
       <c r="G89">
-        <v>-6.252909907060663</v>
+        <v>-7.746628054379823</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.1959158790777</v>
       </c>
       <c r="E90">
-        <v>-27.11764561008764</v>
+        <v>-26.94274235848938</v>
       </c>
       <c r="F90">
-        <v>3.128752132600731</v>
+        <v>2.89293040326222</v>
       </c>
       <c r="G90">
-        <v>-6.604781171338719</v>
+        <v>-8.824581408512993</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.07124403609829</v>
       </c>
       <c r="E91">
-        <v>-27.84127311414332</v>
+        <v>-29.98631615362261</v>
       </c>
       <c r="F91">
-        <v>3.142877205660535</v>
+        <v>3.514794702842335</v>
       </c>
       <c r="G91">
-        <v>-6.242117528602638</v>
+        <v>-7.628547516085098</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.93725790758679</v>
       </c>
       <c r="E92">
-        <v>-29.72146382281</v>
+        <v>-32.11938364358861</v>
       </c>
       <c r="F92">
-        <v>3.246038225286346</v>
+        <v>3.068346421574039</v>
       </c>
       <c r="G92">
-        <v>-6.218020067622284</v>
+        <v>-8.507321897848017</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.78071387845532</v>
       </c>
       <c r="E93">
-        <v>-32.67220390078598</v>
+        <v>-33.29998172399532</v>
       </c>
       <c r="F93">
-        <v>3.115086334256404</v>
+        <v>2.780794522213614</v>
       </c>
       <c r="G93">
-        <v>-5.958585855891758</v>
+        <v>-7.545886504515035</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.59460124789713</v>
       </c>
       <c r="E94">
-        <v>-34.35035900583745</v>
+        <v>-35.08442917095482</v>
       </c>
       <c r="F94">
-        <v>2.918849334274302</v>
+        <v>2.475094936768169</v>
       </c>
       <c r="G94">
-        <v>-5.854230839402851</v>
+        <v>-7.615394718657574</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.37581355267114</v>
       </c>
       <c r="E95">
-        <v>-36.12960323616215</v>
+        <v>-37.16187341468461</v>
       </c>
       <c r="F95">
-        <v>2.972293074096722</v>
+        <v>2.738226090912518</v>
       </c>
       <c r="G95">
-        <v>-5.106206453713448</v>
+        <v>-7.122351860948377</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.10822380540522</v>
       </c>
       <c r="E96">
-        <v>-38.92188068742472</v>
+        <v>-39.73651014090154</v>
       </c>
       <c r="F96">
-        <v>2.900928118135189</v>
+        <v>2.497488538412483</v>
       </c>
       <c r="G96">
-        <v>-5.803238506461458</v>
+        <v>-6.762257201550771</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.793416262177182</v>
       </c>
       <c r="E97">
-        <v>-40.13603928870227</v>
+        <v>-41.47221535787949</v>
       </c>
       <c r="F97">
-        <v>2.675767897019417</v>
+        <v>2.630934766259241</v>
       </c>
       <c r="G97">
-        <v>-6.229408344277377</v>
+        <v>-7.899614984840623</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.424118896957264</v>
       </c>
       <c r="E98">
-        <v>-43.1575345088111</v>
+        <v>-44.80519939836893</v>
       </c>
       <c r="F98">
-        <v>2.740213641836394</v>
+        <v>2.124795025332118</v>
       </c>
       <c r="G98">
-        <v>-6.229630150828508</v>
+        <v>-7.168047321026936</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.008402494801402</v>
       </c>
       <c r="E99">
-        <v>-46.88280666716299</v>
+        <v>-44.93174986875027</v>
       </c>
       <c r="F99">
-        <v>2.433948673379136</v>
+        <v>2.147193378094177</v>
       </c>
       <c r="G99">
-        <v>-6.224694127429455</v>
+        <v>-6.980736654414972</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.53349714181881</v>
       </c>
       <c r="E100">
-        <v>-48.83014785265241</v>
+        <v>-48.11404893663448</v>
       </c>
       <c r="F100">
-        <v>2.755406132683205</v>
+        <v>2.122145485335587</v>
       </c>
       <c r="G100">
-        <v>-6.410293241997615</v>
+        <v>-9.02195944410988</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.04279376257927</v>
       </c>
       <c r="E101">
-        <v>-49.71446599263327</v>
+        <v>-49.48191753115438</v>
       </c>
       <c r="F101">
-        <v>2.108486021814922</v>
+        <v>2.275025368470704</v>
       </c>
       <c r="G101">
-        <v>-6.608426081977457</v>
+        <v>-7.198199769798618</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.485553773181217</v>
       </c>
       <c r="E102">
-        <v>-52.73799562969004</v>
+        <v>-52.86393022760635</v>
       </c>
       <c r="F102">
-        <v>2.281049785773035</v>
+        <v>1.500480732700817</v>
       </c>
       <c r="G102">
-        <v>-6.489935036035862</v>
+        <v>-8.179313045817027</v>
       </c>
     </row>
   </sheetData>
